--- a/data/2026/38-tulcea/159614-tulcea/budget_file.xlsx
+++ b/data/2026/38-tulcea/159614-tulcea/budget_file.xlsx
@@ -36219,11 +36219,11 @@
     <row r="747">
       <c r="A747" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="B747" s="4" t="n"/>
-      <c r="C747" s="8" t="inlineStr">
+      <c r="C747" s="4" t="inlineStr">
         <is>
           <t>Studii, PT,CF Consolidarea și Reabilitarea Energetică Bloc 1A Strada Portului, Nr. 34 Asociația de proprietari Gospodarul din Municipiul Tulcea</t>
         </is>
@@ -36232,7 +36232,11 @@
       <c r="E747" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F747" s="4" t="inlineStr"/>
+      <c r="F747" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G747" s="5" t="n"/>
       <c r="H747" s="5" t="n"/>
       <c r="I747" s="5" t="n"/>
@@ -36256,18 +36260,18 @@
       </c>
       <c r="V747" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026; unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026; unparseable cell '71.01.01 03.30-' in column est2027; name mismatch vs nomenclator (24%): 'Studii, PT,CF Consolidarea și Reabilitar' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="B748" s="4" t="n"/>
-      <c r="C748" s="8" t="inlineStr">
+      <c r="C748" s="4" t="inlineStr">
         <is>
           <t>Studii, PT+ CF Consolidarea și reabilitarea energetică Bloc 1B, Strada Portului. Nr. 32 - Asociația de proprietari Nr. 1 din Municipiul Tulcea</t>
         </is>
@@ -36276,7 +36280,11 @@
       <c r="E748" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F748" s="4" t="inlineStr"/>
+      <c r="F748" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G748" s="5" t="n"/>
       <c r="H748" s="5" t="n"/>
       <c r="I748" s="5" t="n"/>
@@ -36300,7 +36308,7 @@
       </c>
       <c r="V748" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 0330-' in column est2027</t>
+          <t>unparseable cell '71.01.01 0330-' in column est2027; name mismatch vs nomenclator (36%): 'Studii, PT+ CF Consolidarea și reabilita' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -36395,11 +36403,11 @@
     <row r="751">
       <c r="A751" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="B751" s="4" t="n"/>
-      <c r="C751" s="8" t="inlineStr">
+      <c r="C751" s="4" t="inlineStr">
         <is>
           <t>Studii, PT,CF Consolidarea și Reabilitarea energetică Bloc 1C, Strada Portului, NR. 30 - Asociația de proprietari Nr. 2 din Municipiul Tulcea</t>
         </is>
@@ -36408,7 +36416,11 @@
       <c r="E751" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F751" s="4" t="inlineStr"/>
+      <c r="F751" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G751" s="5" t="n"/>
       <c r="H751" s="5" t="n"/>
       <c r="I751" s="5" t="n"/>
@@ -36432,18 +36444,18 @@
       </c>
       <c r="V751" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026; unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026; unparseable cell '71.01.01 03.30-' in column est2027; name mismatch vs nomenclator (23%): 'Studii, PT,CF Consolidarea și Reabilitar' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="B752" s="4" t="n"/>
-      <c r="C752" s="8" t="inlineStr">
+      <c r="C752" s="4" t="inlineStr">
         <is>
           <t>Studii, PT,CF Consolidarea si Reabilitarea Energetică Bloc Belvedere, Strada Frumoasa nr. 1 , Municipiul Tulcea, Județul Tulcea</t>
         </is>
@@ -36452,7 +36464,11 @@
       <c r="E752" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F752" s="4" t="inlineStr"/>
+      <c r="F752" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G752" s="5" t="n"/>
       <c r="H752" s="5" t="n"/>
       <c r="I752" s="5" t="n"/>
@@ -36476,7 +36492,7 @@
       </c>
       <c r="V752" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell '03.30- 71.01.01' in column est2027</t>
+          <t>unparseable cell '03.30- 71.01.01' in column est2027; name mismatch vs nomenclator (39%): 'Studii, PT,CF Consolidarea si Reabilitar' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -36527,11 +36543,11 @@
     <row r="754">
       <c r="A754" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="B754" s="4" t="n"/>
-      <c r="C754" s="8" t="inlineStr">
+      <c r="C754" s="4" t="inlineStr">
         <is>
           <t>Studii, PT,CF Consolidare și reabilitare energetică Bloc 5, Strada Babadag, nr. 11, Municipiul Tulcea, Județ Tulcea</t>
         </is>
@@ -36540,7 +36556,11 @@
       <c r="E754" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F754" s="4" t="inlineStr"/>
+      <c r="F754" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G754" s="5" t="n"/>
       <c r="H754" s="5" t="n"/>
       <c r="I754" s="5" t="n"/>
@@ -36564,7 +36584,7 @@
       </c>
       <c r="V754" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026; unparseable cell '10.10.11 03.30-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026; unparseable cell '10.10.11 03.30-' in column est2027; name mismatch vs nomenclator (29%): 'Studii, PT,CF Consolidare și reabilitare' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -45772,84 +45792,106 @@
       </c>
     </row>
     <row r="1008">
-      <c r="A1008" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C1008" s="2" t="inlineStr">
+      <c r="A1008" s="6" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="B1008" s="6" t="n"/>
+      <c r="C1008" s="6" t="inlineStr">
         <is>
           <t>Colegiul Anghel Saligny Tulcea</t>
         </is>
       </c>
-      <c r="E1008" t="n">
+      <c r="D1008" s="6" t="n"/>
+      <c r="E1008" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="F1008" t="inlineStr"/>
-      <c r="G1008" s="3" t="n"/>
-      <c r="H1008" s="3" t="n">
+      <c r="F1008" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1008" s="7" t="n"/>
+      <c r="H1008" s="7" t="n">
         <v>604</v>
       </c>
-      <c r="I1008" s="3" t="n"/>
-      <c r="J1008" s="3" t="n"/>
-      <c r="K1008" s="3" t="n"/>
-      <c r="L1008" s="3" t="n"/>
-      <c r="M1008" s="3" t="n">
+      <c r="I1008" s="7" t="n"/>
+      <c r="J1008" s="7" t="n"/>
+      <c r="K1008" s="7" t="n"/>
+      <c r="L1008" s="7" t="n"/>
+      <c r="M1008" s="7" t="n">
         <v>2616</v>
       </c>
-      <c r="N1008" s="3" t="n">
+      <c r="N1008" s="7" t="n">
         <v>3220</v>
       </c>
-      <c r="O1008" s="3" t="n"/>
-      <c r="P1008" s="3" t="n"/>
-      <c r="Q1008" s="3" t="n"/>
-      <c r="R1008" s="3" t="n"/>
-      <c r="S1008" s="3" t="n"/>
-      <c r="T1008" s="3" t="n"/>
-      <c r="U1008" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O1008" s="7" t="n"/>
+      <c r="P1008" s="7" t="n"/>
+      <c r="Q1008" s="7" t="n"/>
+      <c r="R1008" s="7" t="n"/>
+      <c r="S1008" s="7" t="n"/>
+      <c r="T1008" s="7" t="n"/>
+      <c r="U1008" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1008" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (42%): 'Colegiul Anghel Saligny Tulcea' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="1009">
-      <c r="A1009" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C1009" s="2" t="inlineStr">
+      <c r="A1009" s="6" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="B1009" s="6" t="n"/>
+      <c r="C1009" s="6" t="inlineStr">
         <is>
           <t>Scoala Gimnaziala Nifon Balasescu Tulcea</t>
         </is>
       </c>
-      <c r="E1009" t="n">
+      <c r="D1009" s="6" t="n"/>
+      <c r="E1009" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="F1009" t="inlineStr"/>
-      <c r="G1009" s="3" t="n"/>
-      <c r="H1009" s="3" t="n">
+      <c r="F1009" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1009" s="7" t="n"/>
+      <c r="H1009" s="7" t="n">
         <v>490</v>
       </c>
-      <c r="I1009" s="3" t="n"/>
-      <c r="J1009" s="3" t="n"/>
-      <c r="K1009" s="3" t="n"/>
-      <c r="L1009" s="3" t="n"/>
-      <c r="M1009" s="3" t="n">
+      <c r="I1009" s="7" t="n"/>
+      <c r="J1009" s="7" t="n"/>
+      <c r="K1009" s="7" t="n"/>
+      <c r="L1009" s="7" t="n"/>
+      <c r="M1009" s="7" t="n">
         <v>2650</v>
       </c>
-      <c r="N1009" s="3" t="n">
+      <c r="N1009" s="7" t="n">
         <v>3140</v>
       </c>
-      <c r="O1009" s="3" t="n"/>
-      <c r="P1009" s="3" t="n"/>
-      <c r="Q1009" s="3" t="n"/>
-      <c r="R1009" s="3" t="n"/>
-      <c r="S1009" s="3" t="n"/>
-      <c r="T1009" s="3" t="n"/>
-      <c r="U1009" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O1009" s="7" t="n"/>
+      <c r="P1009" s="7" t="n"/>
+      <c r="Q1009" s="7" t="n"/>
+      <c r="R1009" s="7" t="n"/>
+      <c r="S1009" s="7" t="n"/>
+      <c r="T1009" s="7" t="n"/>
+      <c r="U1009" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1009" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Scoala Gimnaziala Nifon Balasescu Tulcea' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -45936,84 +45978,106 @@
       </c>
     </row>
     <row r="1012">
-      <c r="A1012" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C1012" s="2" t="inlineStr">
+      <c r="A1012" s="6" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="B1012" s="6" t="n"/>
+      <c r="C1012" s="6" t="inlineStr">
         <is>
           <t>Scoala Gimnaziala Elena Doamna Tulcea</t>
         </is>
       </c>
-      <c r="E1012" t="n">
+      <c r="D1012" s="6" t="n"/>
+      <c r="E1012" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="F1012" t="inlineStr"/>
-      <c r="G1012" s="3" t="n"/>
-      <c r="H1012" s="3" t="n">
+      <c r="F1012" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1012" s="7" t="n"/>
+      <c r="H1012" s="7" t="n">
         <v>553</v>
       </c>
-      <c r="I1012" s="3" t="n"/>
-      <c r="J1012" s="3" t="n"/>
-      <c r="K1012" s="3" t="n"/>
-      <c r="L1012" s="3" t="n"/>
-      <c r="M1012" s="3" t="n">
+      <c r="I1012" s="7" t="n"/>
+      <c r="J1012" s="7" t="n"/>
+      <c r="K1012" s="7" t="n"/>
+      <c r="L1012" s="7" t="n"/>
+      <c r="M1012" s="7" t="n">
         <v>690</v>
       </c>
-      <c r="N1012" s="3" t="n">
+      <c r="N1012" s="7" t="n">
         <v>1343</v>
       </c>
-      <c r="O1012" s="3" t="n"/>
-      <c r="P1012" s="3" t="n"/>
-      <c r="Q1012" s="3" t="n"/>
-      <c r="R1012" s="3" t="n"/>
-      <c r="S1012" s="3" t="n"/>
-      <c r="T1012" s="3" t="n"/>
-      <c r="U1012" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O1012" s="7" t="n"/>
+      <c r="P1012" s="7" t="n"/>
+      <c r="Q1012" s="7" t="n"/>
+      <c r="R1012" s="7" t="n"/>
+      <c r="S1012" s="7" t="n"/>
+      <c r="T1012" s="7" t="n"/>
+      <c r="U1012" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1012" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (32%): 'Scoala Gimnaziala Elena Doamna Tulcea' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="1013">
-      <c r="A1013" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C1013" s="2" t="inlineStr">
+      <c r="A1013" s="6" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="B1013" s="6" t="n"/>
+      <c r="C1013" s="6" t="inlineStr">
         <is>
           <t>Scoala Gimnaziala Constantin Gavenea Tulcea</t>
         </is>
       </c>
-      <c r="E1013" t="n">
+      <c r="D1013" s="6" t="n"/>
+      <c r="E1013" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="F1013" t="inlineStr"/>
-      <c r="G1013" s="3" t="n"/>
-      <c r="H1013" s="3" t="n">
+      <c r="F1013" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1013" s="7" t="n"/>
+      <c r="H1013" s="7" t="n">
         <v>464</v>
       </c>
-      <c r="I1013" s="3" t="n"/>
-      <c r="J1013" s="3" t="n"/>
-      <c r="K1013" s="3" t="n"/>
-      <c r="L1013" s="3" t="n"/>
-      <c r="M1013" s="3" t="n">
+      <c r="I1013" s="7" t="n"/>
+      <c r="J1013" s="7" t="n"/>
+      <c r="K1013" s="7" t="n"/>
+      <c r="L1013" s="7" t="n"/>
+      <c r="M1013" s="7" t="n">
         <v>607</v>
       </c>
-      <c r="N1013" s="3" t="n">
+      <c r="N1013" s="7" t="n">
         <v>1071</v>
       </c>
-      <c r="O1013" s="3" t="n"/>
-      <c r="P1013" s="3" t="n"/>
-      <c r="Q1013" s="3" t="n"/>
-      <c r="R1013" s="3" t="n"/>
-      <c r="S1013" s="3" t="n"/>
-      <c r="T1013" s="3" t="n"/>
-      <c r="U1013" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O1013" s="7" t="n"/>
+      <c r="P1013" s="7" t="n"/>
+      <c r="Q1013" s="7" t="n"/>
+      <c r="R1013" s="7" t="n"/>
+      <c r="S1013" s="7" t="n"/>
+      <c r="T1013" s="7" t="n"/>
+      <c r="U1013" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1013" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (35%): 'Scoala Gimnaziala Constantin Gavenea Tul' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -46059,43 +46123,54 @@
       </c>
     </row>
     <row r="1015">
-      <c r="A1015" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C1015" s="2" t="inlineStr">
+      <c r="A1015" s="6" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="B1015" s="6" t="n"/>
+      <c r="C1015" s="6" t="inlineStr">
         <is>
           <t>Scoala Gimnaziala loan Nenitescu Tulcea</t>
         </is>
       </c>
-      <c r="E1015" t="n">
+      <c r="D1015" s="6" t="n"/>
+      <c r="E1015" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="F1015" t="inlineStr"/>
-      <c r="G1015" s="3" t="n"/>
-      <c r="H1015" s="3" t="n">
+      <c r="F1015" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1015" s="7" t="n"/>
+      <c r="H1015" s="7" t="n">
         <v>391</v>
       </c>
-      <c r="I1015" s="3" t="n"/>
-      <c r="J1015" s="3" t="n"/>
-      <c r="K1015" s="3" t="n"/>
-      <c r="L1015" s="3" t="n"/>
-      <c r="M1015" s="3" t="n">
+      <c r="I1015" s="7" t="n"/>
+      <c r="J1015" s="7" t="n"/>
+      <c r="K1015" s="7" t="n"/>
+      <c r="L1015" s="7" t="n"/>
+      <c r="M1015" s="7" t="n">
         <v>869</v>
       </c>
-      <c r="N1015" s="3" t="n">
+      <c r="N1015" s="7" t="n">
         <v>1260</v>
       </c>
-      <c r="O1015" s="3" t="n"/>
-      <c r="P1015" s="3" t="n"/>
-      <c r="Q1015" s="3" t="n"/>
-      <c r="R1015" s="3" t="n"/>
-      <c r="S1015" s="3" t="n"/>
-      <c r="T1015" s="3" t="n"/>
-      <c r="U1015" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="O1015" s="7" t="n"/>
+      <c r="P1015" s="7" t="n"/>
+      <c r="Q1015" s="7" t="n"/>
+      <c r="R1015" s="7" t="n"/>
+      <c r="S1015" s="7" t="n"/>
+      <c r="T1015" s="7" t="n"/>
+      <c r="U1015" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1015" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (41%): 'Scoala Gimnaziala loan Nenitescu Tulcea' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -47833,98 +47908,98 @@
       </c>
     </row>
     <row r="1066">
-      <c r="A1066" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B1066" s="4" t="n"/>
-      <c r="C1066" s="4" t="inlineStr">
+      <c r="A1066" s="6" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="B1066" s="6" t="n"/>
+      <c r="C1066" s="6" t="inlineStr">
         <is>
           <t>Container modular - Liceul Grigore Moisil</t>
         </is>
       </c>
-      <c r="D1066" s="4" t="n"/>
-      <c r="E1066" s="4" t="n">
+      <c r="D1066" s="6" t="n"/>
+      <c r="E1066" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F1066" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1066" s="5" t="n"/>
-      <c r="H1066" s="5" t="n">
+      <c r="F1066" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1066" s="7" t="n"/>
+      <c r="H1066" s="7" t="n">
         <v>70000</v>
       </c>
-      <c r="I1066" s="5" t="n"/>
-      <c r="J1066" s="5" t="n"/>
-      <c r="K1066" s="5" t="n"/>
-      <c r="L1066" s="5" t="n"/>
-      <c r="M1066" s="5" t="n"/>
-      <c r="N1066" s="5" t="n"/>
-      <c r="O1066" s="5" t="n"/>
-      <c r="P1066" s="5" t="n"/>
-      <c r="Q1066" s="5" t="n"/>
-      <c r="R1066" s="5" t="n"/>
-      <c r="S1066" s="5" t="n"/>
-      <c r="T1066" s="5" t="n"/>
-      <c r="U1066" s="4" t="inlineStr">
+      <c r="I1066" s="7" t="n"/>
+      <c r="J1066" s="7" t="n"/>
+      <c r="K1066" s="7" t="n"/>
+      <c r="L1066" s="7" t="n"/>
+      <c r="M1066" s="7" t="n"/>
+      <c r="N1066" s="7" t="n"/>
+      <c r="O1066" s="7" t="n"/>
+      <c r="P1066" s="7" t="n"/>
+      <c r="Q1066" s="7" t="n"/>
+      <c r="R1066" s="7" t="n"/>
+      <c r="S1066" s="7" t="n"/>
+      <c r="T1066" s="7" t="n"/>
+      <c r="U1066" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1066" s="4" t="inlineStr">
-        <is>
-          <t>code 11 (expense_functional) not in nomenclator</t>
+      <c r="V1066" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (29%): 'Container modular - Liceul Grigore Moisi' vs 'Sume defalcate din TVA'; duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="1067">
-      <c r="A1067" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B1067" s="4" t="n"/>
-      <c r="C1067" s="4" t="inlineStr">
+      <c r="A1067" s="6" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="B1067" s="6" t="n"/>
+      <c r="C1067" s="6" t="inlineStr">
         <is>
           <t>Laptopuri 10 buc - Liceul Grigore Moisil</t>
         </is>
       </c>
-      <c r="D1067" s="4" t="n"/>
-      <c r="E1067" s="4" t="n">
+      <c r="D1067" s="6" t="n"/>
+      <c r="E1067" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F1067" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1067" s="5" t="n"/>
-      <c r="H1067" s="5" t="n">
+      <c r="F1067" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1067" s="7" t="n"/>
+      <c r="H1067" s="7" t="n">
         <v>50000</v>
       </c>
-      <c r="I1067" s="5" t="n"/>
-      <c r="J1067" s="5" t="n"/>
-      <c r="K1067" s="5" t="n"/>
-      <c r="L1067" s="5" t="n"/>
-      <c r="M1067" s="5" t="n"/>
-      <c r="N1067" s="5" t="n"/>
-      <c r="O1067" s="5" t="n"/>
-      <c r="P1067" s="5" t="n"/>
-      <c r="Q1067" s="5" t="n"/>
-      <c r="R1067" s="5" t="n"/>
-      <c r="S1067" s="5" t="n"/>
-      <c r="T1067" s="5" t="n"/>
-      <c r="U1067" s="4" t="inlineStr">
+      <c r="I1067" s="7" t="n"/>
+      <c r="J1067" s="7" t="n"/>
+      <c r="K1067" s="7" t="n"/>
+      <c r="L1067" s="7" t="n"/>
+      <c r="M1067" s="7" t="n"/>
+      <c r="N1067" s="7" t="n"/>
+      <c r="O1067" s="7" t="n"/>
+      <c r="P1067" s="7" t="n"/>
+      <c r="Q1067" s="7" t="n"/>
+      <c r="R1067" s="7" t="n"/>
+      <c r="S1067" s="7" t="n"/>
+      <c r="T1067" s="7" t="n"/>
+      <c r="U1067" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1067" s="4" t="inlineStr">
-        <is>
-          <t>code 12 (expense_functional) not in nomenclator</t>
+      <c r="V1067" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Laptopuri 10 buc - Liceul Grigore Moisil' vs 'Alte impozite si taxe generale pe bunuri'; duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -48025,98 +48100,98 @@
       </c>
     </row>
     <row r="1070">
-      <c r="A1070" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B1070" s="4" t="n"/>
-      <c r="C1070" s="4" t="inlineStr">
+      <c r="A1070" s="6" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="B1070" s="6" t="n"/>
+      <c r="C1070" s="6" t="inlineStr">
         <is>
           <t>Table interactive - 3 buc - Scoala gimnaziala Alexandru Ciucurencu</t>
         </is>
       </c>
-      <c r="D1070" s="4" t="n"/>
-      <c r="E1070" s="4" t="n">
+      <c r="D1070" s="6" t="n"/>
+      <c r="E1070" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F1070" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1070" s="5" t="n"/>
-      <c r="H1070" s="5" t="n">
+      <c r="F1070" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1070" s="7" t="n"/>
+      <c r="H1070" s="7" t="n">
         <v>32000</v>
       </c>
-      <c r="I1070" s="5" t="n"/>
-      <c r="J1070" s="5" t="n"/>
-      <c r="K1070" s="5" t="n"/>
-      <c r="L1070" s="5" t="n"/>
-      <c r="M1070" s="5" t="n"/>
-      <c r="N1070" s="5" t="n"/>
-      <c r="O1070" s="5" t="n"/>
-      <c r="P1070" s="5" t="n"/>
-      <c r="Q1070" s="5" t="n"/>
-      <c r="R1070" s="5" t="n"/>
-      <c r="S1070" s="5" t="n"/>
-      <c r="T1070" s="5" t="n"/>
-      <c r="U1070" s="4" t="inlineStr">
+      <c r="I1070" s="7" t="n"/>
+      <c r="J1070" s="7" t="n"/>
+      <c r="K1070" s="7" t="n"/>
+      <c r="L1070" s="7" t="n"/>
+      <c r="M1070" s="7" t="n"/>
+      <c r="N1070" s="7" t="n"/>
+      <c r="O1070" s="7" t="n"/>
+      <c r="P1070" s="7" t="n"/>
+      <c r="Q1070" s="7" t="n"/>
+      <c r="R1070" s="7" t="n"/>
+      <c r="S1070" s="7" t="n"/>
+      <c r="T1070" s="7" t="n"/>
+      <c r="U1070" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1070" s="4" t="inlineStr">
-        <is>
-          <t>code 15 (expense_functional) not in nomenclator</t>
+      <c r="V1070" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (36%): 'Table interactive - 3 buc - Scoala gimna' vs 'Taxe pe servicii specifice'; duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="1071">
-      <c r="A1071" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B1071" s="4" t="n"/>
-      <c r="C1071" s="4" t="inlineStr">
+      <c r="A1071" s="6" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="B1071" s="6" t="n"/>
+      <c r="C1071" s="6" t="inlineStr">
         <is>
           <t>Table inteligente - Scoala gimnaziala Nr 12</t>
         </is>
       </c>
-      <c r="D1071" s="4" t="n"/>
-      <c r="E1071" s="4" t="n">
+      <c r="D1071" s="6" t="n"/>
+      <c r="E1071" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F1071" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1071" s="5" t="n"/>
-      <c r="H1071" s="5" t="n">
+      <c r="F1071" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1071" s="7" t="n"/>
+      <c r="H1071" s="7" t="n">
         <v>72000</v>
       </c>
-      <c r="I1071" s="5" t="n"/>
-      <c r="J1071" s="5" t="n"/>
-      <c r="K1071" s="5" t="n"/>
-      <c r="L1071" s="5" t="n"/>
-      <c r="M1071" s="5" t="n"/>
-      <c r="N1071" s="5" t="n"/>
-      <c r="O1071" s="5" t="n"/>
-      <c r="P1071" s="5" t="n"/>
-      <c r="Q1071" s="5" t="n"/>
-      <c r="R1071" s="5" t="n"/>
-      <c r="S1071" s="5" t="n"/>
-      <c r="T1071" s="5" t="n"/>
-      <c r="U1071" s="4" t="inlineStr">
+      <c r="I1071" s="7" t="n"/>
+      <c r="J1071" s="7" t="n"/>
+      <c r="K1071" s="7" t="n"/>
+      <c r="L1071" s="7" t="n"/>
+      <c r="M1071" s="7" t="n"/>
+      <c r="N1071" s="7" t="n"/>
+      <c r="O1071" s="7" t="n"/>
+      <c r="P1071" s="7" t="n"/>
+      <c r="Q1071" s="7" t="n"/>
+      <c r="R1071" s="7" t="n"/>
+      <c r="S1071" s="7" t="n"/>
+      <c r="T1071" s="7" t="n"/>
+      <c r="U1071" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1071" s="4" t="inlineStr">
-        <is>
-          <t>code 16 (expense_functional) not in nomenclator</t>
+      <c r="V1071" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (29%): 'Table inteligente - Scoala gimnaziala Nr' vs 'Taxe pe utilizarea bunurilor, autorizare'; duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -48169,50 +48244,50 @@
       </c>
     </row>
     <row r="1073">
-      <c r="A1073" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B1073" s="4" t="n"/>
-      <c r="C1073" s="4" t="inlineStr">
+      <c r="A1073" s="6" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="B1073" s="6" t="n"/>
+      <c r="C1073" s="6" t="inlineStr">
         <is>
           <t>Masini de gatit pe gaz - 2 buc - Liceul Ion Creanga</t>
         </is>
       </c>
-      <c r="D1073" s="4" t="n"/>
-      <c r="E1073" s="4" t="n">
+      <c r="D1073" s="6" t="n"/>
+      <c r="E1073" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F1073" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1073" s="5" t="n"/>
-      <c r="H1073" s="5" t="n">
+      <c r="F1073" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1073" s="7" t="n"/>
+      <c r="H1073" s="7" t="n">
         <v>25000</v>
       </c>
-      <c r="I1073" s="5" t="n"/>
-      <c r="J1073" s="5" t="n"/>
-      <c r="K1073" s="5" t="n"/>
-      <c r="L1073" s="5" t="n"/>
-      <c r="M1073" s="5" t="n"/>
-      <c r="N1073" s="5" t="n"/>
-      <c r="O1073" s="5" t="n"/>
-      <c r="P1073" s="5" t="n"/>
-      <c r="Q1073" s="5" t="n"/>
-      <c r="R1073" s="5" t="n"/>
-      <c r="S1073" s="5" t="n"/>
-      <c r="T1073" s="5" t="n"/>
-      <c r="U1073" s="4" t="inlineStr">
+      <c r="I1073" s="7" t="n"/>
+      <c r="J1073" s="7" t="n"/>
+      <c r="K1073" s="7" t="n"/>
+      <c r="L1073" s="7" t="n"/>
+      <c r="M1073" s="7" t="n"/>
+      <c r="N1073" s="7" t="n"/>
+      <c r="O1073" s="7" t="n"/>
+      <c r="P1073" s="7" t="n"/>
+      <c r="Q1073" s="7" t="n"/>
+      <c r="R1073" s="7" t="n"/>
+      <c r="S1073" s="7" t="n"/>
+      <c r="T1073" s="7" t="n"/>
+      <c r="U1073" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1073" s="4" t="inlineStr">
-        <is>
-          <t>code 18 (expense_functional) not in nomenclator</t>
+      <c r="V1073" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (38%): 'Masini de gatit pe gaz - 2 buc - Liceul ' vs 'Alte impozite si taxe fiscale'; duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -48797,50 +48872,50 @@
       </c>
     </row>
     <row r="1086">
-      <c r="A1086" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B1086" s="4" t="n"/>
-      <c r="C1086" s="4" t="inlineStr">
+      <c r="A1086" s="6" t="inlineStr">
+        <is>
+          <t>31.02</t>
+        </is>
+      </c>
+      <c r="B1086" s="6" t="n"/>
+      <c r="C1086" s="6" t="inlineStr">
         <is>
           <t>Studii,SF, Construire Cresa cartier E3, municipiul Tulcea</t>
         </is>
       </c>
-      <c r="D1086" s="4" t="n"/>
-      <c r="E1086" s="4" t="n">
+      <c r="D1086" s="6" t="n"/>
+      <c r="E1086" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F1086" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1086" s="5" t="n"/>
-      <c r="H1086" s="5" t="n">
+      <c r="F1086" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1086" s="7" t="n"/>
+      <c r="H1086" s="7" t="n">
         <v>12000</v>
       </c>
-      <c r="I1086" s="5" t="n"/>
-      <c r="J1086" s="5" t="n"/>
-      <c r="K1086" s="5" t="n"/>
-      <c r="L1086" s="5" t="n"/>
-      <c r="M1086" s="5" t="n"/>
-      <c r="N1086" s="5" t="n"/>
-      <c r="O1086" s="5" t="n"/>
-      <c r="P1086" s="5" t="n"/>
-      <c r="Q1086" s="5" t="n"/>
-      <c r="R1086" s="5" t="n"/>
-      <c r="S1086" s="5" t="n"/>
-      <c r="T1086" s="5" t="n"/>
-      <c r="U1086" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="V1086" s="4" t="inlineStr">
-        <is>
-          <t>code 31 (expense_functional) not in nomenclator</t>
+      <c r="I1086" s="7" t="n"/>
+      <c r="J1086" s="7" t="n"/>
+      <c r="K1086" s="7" t="n"/>
+      <c r="L1086" s="7" t="n"/>
+      <c r="M1086" s="7" t="n"/>
+      <c r="N1086" s="7" t="n"/>
+      <c r="O1086" s="7" t="n"/>
+      <c r="P1086" s="7" t="n"/>
+      <c r="Q1086" s="7" t="n"/>
+      <c r="R1086" s="7" t="n"/>
+      <c r="S1086" s="7" t="n"/>
+      <c r="T1086" s="7" t="n"/>
+      <c r="U1086" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1086" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Studii,SF, Construire Cresa cartier E3, ' vs 'Venituri din dobanzi'</t>
         </is>
       </c>
     </row>
@@ -48893,50 +48968,50 @@
       </c>
     </row>
     <row r="1088">
-      <c r="A1088" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B1088" s="4" t="n"/>
-      <c r="C1088" s="4" t="inlineStr">
+      <c r="A1088" s="6" t="inlineStr">
+        <is>
+          <t>33.02</t>
+        </is>
+      </c>
+      <c r="B1088" s="6" t="n"/>
+      <c r="C1088" s="6" t="inlineStr">
         <is>
           <t>Modernizarea infrastructurii scolare prin GAL RESTART-NEPTUN Tulcea</t>
         </is>
       </c>
-      <c r="D1088" s="4" t="n"/>
-      <c r="E1088" s="4" t="n">
+      <c r="D1088" s="6" t="n"/>
+      <c r="E1088" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F1088" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1088" s="5" t="n"/>
-      <c r="H1088" s="5" t="n">
+      <c r="F1088" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1088" s="7" t="n"/>
+      <c r="H1088" s="7" t="n">
         <v>415000</v>
       </c>
-      <c r="I1088" s="5" t="n"/>
-      <c r="J1088" s="5" t="n"/>
-      <c r="K1088" s="5" t="n"/>
-      <c r="L1088" s="5" t="n"/>
-      <c r="M1088" s="5" t="n"/>
-      <c r="N1088" s="5" t="n"/>
-      <c r="O1088" s="5" t="n"/>
-      <c r="P1088" s="5" t="n"/>
-      <c r="Q1088" s="5" t="n"/>
-      <c r="R1088" s="5" t="n"/>
-      <c r="S1088" s="5" t="n"/>
-      <c r="T1088" s="5" t="n"/>
-      <c r="U1088" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="V1088" s="4" t="inlineStr">
-        <is>
-          <t>code 33 (expense_functional) not in nomenclator</t>
+      <c r="I1088" s="7" t="n"/>
+      <c r="J1088" s="7" t="n"/>
+      <c r="K1088" s="7" t="n"/>
+      <c r="L1088" s="7" t="n"/>
+      <c r="M1088" s="7" t="n"/>
+      <c r="N1088" s="7" t="n"/>
+      <c r="O1088" s="7" t="n"/>
+      <c r="P1088" s="7" t="n"/>
+      <c r="Q1088" s="7" t="n"/>
+      <c r="R1088" s="7" t="n"/>
+      <c r="S1088" s="7" t="n"/>
+      <c r="T1088" s="7" t="n"/>
+      <c r="U1088" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1088" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Modernizarea infrastructurii scolare pri' vs 'Venituri din prestari de servicii si alt'</t>
         </is>
       </c>
     </row>
@@ -48987,96 +49062,96 @@
       </c>
     </row>
     <row r="1090">
-      <c r="A1090" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B1090" s="4" t="n"/>
-      <c r="C1090" s="4" t="inlineStr">
+      <c r="A1090" s="6" t="inlineStr">
+        <is>
+          <t>36.02</t>
+        </is>
+      </c>
+      <c r="B1090" s="6" t="n"/>
+      <c r="C1090" s="6" t="inlineStr">
         <is>
           <t>Stagii de practica pt elevi in Delta Dunarii Modernizare Grădinița cu program prelungit nr. 19 Dumbrava Minunată str. Libertății nr. 76, Municipiul Tulcea-ctr.135990</t>
         </is>
       </c>
-      <c r="D1090" s="4" t="n"/>
-      <c r="E1090" s="4" t="n">
+      <c r="D1090" s="6" t="n"/>
+      <c r="E1090" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F1090" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1090" s="5" t="n"/>
-      <c r="H1090" s="5" t="n"/>
-      <c r="I1090" s="5" t="n"/>
-      <c r="J1090" s="5" t="n"/>
-      <c r="K1090" s="5" t="n"/>
-      <c r="L1090" s="5" t="n"/>
-      <c r="M1090" s="5" t="n"/>
-      <c r="N1090" s="5" t="n"/>
-      <c r="O1090" s="5" t="n"/>
-      <c r="P1090" s="5" t="n"/>
-      <c r="Q1090" s="5" t="n"/>
-      <c r="R1090" s="5" t="n"/>
-      <c r="S1090" s="5" t="n"/>
-      <c r="T1090" s="5" t="n"/>
-      <c r="U1090" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="V1090" s="4" t="inlineStr">
-        <is>
-          <t>code 36 (expense_functional) not in nomenclator</t>
+      <c r="F1090" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1090" s="7" t="n"/>
+      <c r="H1090" s="7" t="n"/>
+      <c r="I1090" s="7" t="n"/>
+      <c r="J1090" s="7" t="n"/>
+      <c r="K1090" s="7" t="n"/>
+      <c r="L1090" s="7" t="n"/>
+      <c r="M1090" s="7" t="n"/>
+      <c r="N1090" s="7" t="n"/>
+      <c r="O1090" s="7" t="n"/>
+      <c r="P1090" s="7" t="n"/>
+      <c r="Q1090" s="7" t="n"/>
+      <c r="R1090" s="7" t="n"/>
+      <c r="S1090" s="7" t="n"/>
+      <c r="T1090" s="7" t="n"/>
+      <c r="U1090" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1090" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (15%): 'Stagii de practica pt elevi in Delta Dun' vs 'Diverse venituri'</t>
         </is>
       </c>
     </row>
     <row r="1091">
-      <c r="A1091" s="4" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B1091" s="4" t="n"/>
-      <c r="C1091" s="4" t="inlineStr">
+      <c r="A1091" s="6" t="inlineStr">
+        <is>
+          <t>37.02</t>
+        </is>
+      </c>
+      <c r="B1091" s="6" t="n"/>
+      <c r="C1091" s="6" t="inlineStr">
         <is>
           <t>George Georgescu, str. Babadag, nr. 138, Municipiul Tulcea-ctr.135991 Reabilitare camin internat si cantina scoala Liceul</t>
         </is>
       </c>
-      <c r="D1091" s="4" t="n"/>
-      <c r="E1091" s="4" t="n">
+      <c r="D1091" s="6" t="n"/>
+      <c r="E1091" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F1091" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1091" s="5" t="n"/>
-      <c r="H1091" s="5" t="n">
+      <c r="F1091" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1091" s="7" t="n"/>
+      <c r="H1091" s="7" t="n">
         <v>378000</v>
       </c>
-      <c r="I1091" s="5" t="n"/>
-      <c r="J1091" s="5" t="n"/>
-      <c r="K1091" s="5" t="n"/>
-      <c r="L1091" s="5" t="n"/>
-      <c r="M1091" s="5" t="n"/>
-      <c r="N1091" s="5" t="n"/>
-      <c r="O1091" s="5" t="n"/>
-      <c r="P1091" s="5" t="n"/>
-      <c r="Q1091" s="5" t="n"/>
-      <c r="R1091" s="5" t="n"/>
-      <c r="S1091" s="5" t="n"/>
-      <c r="T1091" s="5" t="n"/>
-      <c r="U1091" s="4" t="inlineStr">
+      <c r="I1091" s="7" t="n"/>
+      <c r="J1091" s="7" t="n"/>
+      <c r="K1091" s="7" t="n"/>
+      <c r="L1091" s="7" t="n"/>
+      <c r="M1091" s="7" t="n"/>
+      <c r="N1091" s="7" t="n"/>
+      <c r="O1091" s="7" t="n"/>
+      <c r="P1091" s="7" t="n"/>
+      <c r="Q1091" s="7" t="n"/>
+      <c r="R1091" s="7" t="n"/>
+      <c r="S1091" s="7" t="n"/>
+      <c r="T1091" s="7" t="n"/>
+      <c r="U1091" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="V1091" s="4" t="inlineStr">
-        <is>
-          <t>code 37 (expense_functional) not in nomenclator; cell re-read from image (unverified transcription)</t>
+      <c r="V1091" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'George Georgescu, str. Babadag, nr. 138,' vs 'Transferuri voluntare,  altele decat sub'; cell re-read from image (unverified transcription)</t>
         </is>
       </c>
     </row>
@@ -49127,48 +49202,48 @@
       </c>
     </row>
     <row r="1093">
-      <c r="A1093" s="4" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B1093" s="4" t="n"/>
-      <c r="C1093" s="4" t="inlineStr">
+      <c r="A1093" s="6" t="inlineStr">
+        <is>
+          <t>39.02</t>
+        </is>
+      </c>
+      <c r="B1093" s="6" t="n"/>
+      <c r="C1093" s="6" t="inlineStr">
         <is>
           <t>Reabilitare si modernizare Scoala I.L.Caragiale, Municipiul Tulcea-ctr.7800 Dotarea cu mobilier, materiale didactice și</t>
         </is>
       </c>
-      <c r="D1093" s="4" t="n"/>
-      <c r="E1093" s="4" t="n">
+      <c r="D1093" s="6" t="n"/>
+      <c r="E1093" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="F1093" s="4" t="inlineStr">
-        <is>
-          <t>expense_functional</t>
-        </is>
-      </c>
-      <c r="G1093" s="5" t="n"/>
-      <c r="H1093" s="5" t="n"/>
-      <c r="I1093" s="5" t="n"/>
-      <c r="J1093" s="5" t="n"/>
-      <c r="K1093" s="5" t="n"/>
-      <c r="L1093" s="5" t="n"/>
-      <c r="M1093" s="5" t="n"/>
-      <c r="N1093" s="5" t="n"/>
-      <c r="O1093" s="5" t="n"/>
-      <c r="P1093" s="5" t="n"/>
-      <c r="Q1093" s="5" t="n"/>
-      <c r="R1093" s="5" t="n"/>
-      <c r="S1093" s="5" t="n"/>
-      <c r="T1093" s="5" t="n"/>
-      <c r="U1093" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="V1093" s="4" t="inlineStr">
-        <is>
-          <t>code 39 (expense_functional) not in nomenclator</t>
+      <c r="F1093" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1093" s="7" t="n"/>
+      <c r="H1093" s="7" t="n"/>
+      <c r="I1093" s="7" t="n"/>
+      <c r="J1093" s="7" t="n"/>
+      <c r="K1093" s="7" t="n"/>
+      <c r="L1093" s="7" t="n"/>
+      <c r="M1093" s="7" t="n"/>
+      <c r="N1093" s="7" t="n"/>
+      <c r="O1093" s="7" t="n"/>
+      <c r="P1093" s="7" t="n"/>
+      <c r="Q1093" s="7" t="n"/>
+      <c r="R1093" s="7" t="n"/>
+      <c r="S1093" s="7" t="n"/>
+      <c r="T1093" s="7" t="n"/>
+      <c r="U1093" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1093" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Reabilitare si modernizare Scoala I.L.Ca' vs 'Venituri din valorificarea unor bunuri'</t>
         </is>
       </c>
     </row>
@@ -49301,11 +49376,11 @@
     <row r="1098">
       <c r="A1098" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="B1098" s="4" t="n"/>
-      <c r="C1098" s="8" t="inlineStr">
+      <c r="C1098" s="4" t="inlineStr">
         <is>
           <t>Amenajare teren sintetic stadion Cozma Zait, municipiul Tulcea Generator curen Heavy Duty</t>
         </is>
@@ -49314,7 +49389,11 @@
       <c r="E1098" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="F1098" s="4" t="inlineStr"/>
+      <c r="F1098" s="4" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
       <c r="G1098" s="5" t="n"/>
       <c r="H1098" s="5" t="n"/>
       <c r="I1098" s="5" t="n"/>
@@ -49336,7 +49415,7 @@
       </c>
       <c r="V1098" s="4" t="inlineStr">
         <is>
-          <t>unparseable cell '100.000,00 30.000,00' in column total_2026</t>
+          <t>unparseable cell '100.000,00 30.000,00' in column total_2026; name mismatch vs nomenclator (41%): 'Amenajare teren sintetic stadion Cozma Z' vs 'Venituri din taxe administrative, eliber'</t>
         </is>
       </c>
     </row>
@@ -50017,76 +50096,98 @@
       </c>
     </row>
     <row r="1118">
-      <c r="A1118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C1118" s="2" t="inlineStr">
+      <c r="A1118" s="6" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="B1118" s="6" t="n"/>
+      <c r="C1118" s="6" t="inlineStr">
         <is>
           <t>Centru comunitar integrat, Municipiul Tulcea - Măsuri integrate pentru o societate incluzivă</t>
         </is>
       </c>
-      <c r="E1118" t="n">
+      <c r="D1118" s="6" t="n"/>
+      <c r="E1118" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="F1118" t="inlineStr"/>
-      <c r="G1118" s="3" t="n"/>
-      <c r="H1118" s="3" t="n">
+      <c r="F1118" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1118" s="7" t="n"/>
+      <c r="H1118" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="I1118" s="3" t="n"/>
-      <c r="J1118" s="3" t="n"/>
-      <c r="K1118" s="3" t="n"/>
-      <c r="L1118" s="3" t="n"/>
-      <c r="M1118" s="3" t="n"/>
-      <c r="N1118" s="3" t="n"/>
-      <c r="O1118" s="3" t="n"/>
-      <c r="P1118" s="3" t="n"/>
-      <c r="Q1118" s="3" t="n"/>
-      <c r="R1118" s="3" t="n"/>
-      <c r="S1118" s="3" t="n"/>
-      <c r="T1118" s="3" t="n"/>
-      <c r="U1118" t="inlineStr">
+      <c r="I1118" s="7" t="n"/>
+      <c r="J1118" s="7" t="n"/>
+      <c r="K1118" s="7" t="n"/>
+      <c r="L1118" s="7" t="n"/>
+      <c r="M1118" s="7" t="n"/>
+      <c r="N1118" s="7" t="n"/>
+      <c r="O1118" s="7" t="n"/>
+      <c r="P1118" s="7" t="n"/>
+      <c r="Q1118" s="7" t="n"/>
+      <c r="R1118" s="7" t="n"/>
+      <c r="S1118" s="7" t="n"/>
+      <c r="T1118" s="7" t="n"/>
+      <c r="U1118" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
+      <c r="V1118" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (30%): 'Centru comunitar integrat, Municipiul Tu' vs 'Sume defalcate din TVA'</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
-      <c r="A1119" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C1119" s="2" t="inlineStr">
+      <c r="A1119" s="6" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="B1119" s="6" t="n"/>
+      <c r="C1119" s="6" t="inlineStr">
         <is>
           <t>Elaborare studiu de fezabilitate construire Centru de Asistenta Integrata Comunitara-DAPS</t>
         </is>
       </c>
-      <c r="E1119" t="n">
+      <c r="D1119" s="6" t="n"/>
+      <c r="E1119" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="F1119" t="inlineStr"/>
-      <c r="G1119" s="3" t="n"/>
-      <c r="H1119" s="3" t="n">
+      <c r="F1119" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1119" s="7" t="n"/>
+      <c r="H1119" s="7" t="n">
         <v>75500</v>
       </c>
-      <c r="I1119" s="3" t="n"/>
-      <c r="J1119" s="3" t="n"/>
-      <c r="K1119" s="3" t="n"/>
-      <c r="L1119" s="3" t="n"/>
-      <c r="M1119" s="3" t="n"/>
-      <c r="N1119" s="3" t="n"/>
-      <c r="O1119" s="3" t="n"/>
-      <c r="P1119" s="3" t="n"/>
-      <c r="Q1119" s="3" t="n"/>
-      <c r="R1119" s="3" t="n"/>
-      <c r="S1119" s="3" t="n"/>
-      <c r="T1119" s="3" t="n"/>
-      <c r="U1119" t="inlineStr">
+      <c r="I1119" s="7" t="n"/>
+      <c r="J1119" s="7" t="n"/>
+      <c r="K1119" s="7" t="n"/>
+      <c r="L1119" s="7" t="n"/>
+      <c r="M1119" s="7" t="n"/>
+      <c r="N1119" s="7" t="n"/>
+      <c r="O1119" s="7" t="n"/>
+      <c r="P1119" s="7" t="n"/>
+      <c r="Q1119" s="7" t="n"/>
+      <c r="R1119" s="7" t="n"/>
+      <c r="S1119" s="7" t="n"/>
+      <c r="T1119" s="7" t="n"/>
+      <c r="U1119" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
+        </is>
+      </c>
+      <c r="V1119" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (37%): 'Elaborare studiu de fezabilitate constru' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -50165,76 +50266,98 @@
       </c>
     </row>
     <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C1122" s="2" t="inlineStr">
+      <c r="A1122" s="6" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="B1122" s="6" t="n"/>
+      <c r="C1122" s="6" t="inlineStr">
         <is>
           <t>Centru de recuperare neuromotorie de tip ambulatoriu pentru persoanele adulte cu dizabilitati "Sf Mihail"-DAPS</t>
         </is>
       </c>
-      <c r="E1122" t="n">
+      <c r="D1122" s="6" t="n"/>
+      <c r="E1122" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="F1122" t="inlineStr"/>
-      <c r="G1122" s="3" t="n"/>
-      <c r="H1122" s="3" t="n"/>
-      <c r="I1122" s="3" t="n"/>
-      <c r="J1122" s="3" t="n"/>
-      <c r="K1122" s="3" t="n"/>
-      <c r="L1122" s="3" t="n"/>
-      <c r="M1122" s="3" t="n"/>
-      <c r="N1122" s="3" t="n"/>
-      <c r="O1122" s="3" t="n">
+      <c r="F1122" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1122" s="7" t="n"/>
+      <c r="H1122" s="7" t="n"/>
+      <c r="I1122" s="7" t="n"/>
+      <c r="J1122" s="7" t="n"/>
+      <c r="K1122" s="7" t="n"/>
+      <c r="L1122" s="7" t="n"/>
+      <c r="M1122" s="7" t="n"/>
+      <c r="N1122" s="7" t="n"/>
+      <c r="O1122" s="7" t="n">
         <v>2440000</v>
       </c>
-      <c r="P1122" s="3" t="n"/>
-      <c r="Q1122" s="3" t="n"/>
-      <c r="R1122" s="3" t="n"/>
-      <c r="S1122" s="3" t="n"/>
-      <c r="T1122" s="3" t="n"/>
-      <c r="U1122" t="inlineStr">
+      <c r="P1122" s="7" t="n"/>
+      <c r="Q1122" s="7" t="n"/>
+      <c r="R1122" s="7" t="n"/>
+      <c r="S1122" s="7" t="n"/>
+      <c r="T1122" s="7" t="n"/>
+      <c r="U1122" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
         </is>
       </c>
+      <c r="V1122" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (24%): 'Centru de recuperare neuromotorie de tip' vs 'Taxe pe servicii specifice'</t>
+        </is>
+      </c>
     </row>
     <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C1123" s="2" t="inlineStr">
+      <c r="A1123" s="6" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="B1123" s="6" t="n"/>
+      <c r="C1123" s="6" t="inlineStr">
         <is>
           <t>Centru de zi pentru persoane adulte cu dizabilitati "Sf Gavril"-DAPS</t>
         </is>
       </c>
-      <c r="E1123" t="n">
+      <c r="D1123" s="6" t="n"/>
+      <c r="E1123" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="F1123" t="inlineStr"/>
-      <c r="G1123" s="3" t="n"/>
-      <c r="H1123" s="3" t="n"/>
-      <c r="I1123" s="3" t="n"/>
-      <c r="J1123" s="3" t="n"/>
-      <c r="K1123" s="3" t="n"/>
-      <c r="L1123" s="3" t="n"/>
-      <c r="M1123" s="3" t="n"/>
-      <c r="N1123" s="3" t="n"/>
-      <c r="O1123" s="3" t="n">
+      <c r="F1123" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1123" s="7" t="n"/>
+      <c r="H1123" s="7" t="n"/>
+      <c r="I1123" s="7" t="n"/>
+      <c r="J1123" s="7" t="n"/>
+      <c r="K1123" s="7" t="n"/>
+      <c r="L1123" s="7" t="n"/>
+      <c r="M1123" s="7" t="n"/>
+      <c r="N1123" s="7" t="n"/>
+      <c r="O1123" s="7" t="n">
         <v>3260000</v>
       </c>
-      <c r="P1123" s="3" t="n"/>
-      <c r="Q1123" s="3" t="n"/>
-      <c r="R1123" s="3" t="n"/>
-      <c r="S1123" s="3" t="n"/>
-      <c r="T1123" s="3" t="n"/>
-      <c r="U1123" t="inlineStr">
+      <c r="P1123" s="7" t="n"/>
+      <c r="Q1123" s="7" t="n"/>
+      <c r="R1123" s="7" t="n"/>
+      <c r="S1123" s="7" t="n"/>
+      <c r="T1123" s="7" t="n"/>
+      <c r="U1123" s="6" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
+        </is>
+      </c>
+      <c r="V1123" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Centru de zi pentru persoane adulte cu d' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -51474,76 +51597,98 @@
       </c>
     </row>
     <row r="1162">
-      <c r="A1162" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C1162" s="2" t="inlineStr">
+      <c r="A1162" s="6" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="B1162" s="6" t="n"/>
+      <c r="C1162" s="6" t="inlineStr">
         <is>
           <t>Modernizare strazi și rețele tehnico-edilitare cartier C.A.P.</t>
         </is>
       </c>
-      <c r="E1162" t="n">
+      <c r="D1162" s="6" t="n"/>
+      <c r="E1162" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F1162" t="inlineStr"/>
-      <c r="G1162" s="3" t="n"/>
-      <c r="H1162" s="3" t="n">
+      <c r="F1162" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1162" s="7" t="n"/>
+      <c r="H1162" s="7" t="n">
         <v>305000</v>
       </c>
-      <c r="I1162" s="3" t="n"/>
-      <c r="J1162" s="3" t="n"/>
-      <c r="K1162" s="3" t="n"/>
-      <c r="L1162" s="3" t="n"/>
-      <c r="M1162" s="3" t="n"/>
-      <c r="N1162" s="3" t="n"/>
-      <c r="O1162" s="3" t="n"/>
-      <c r="P1162" s="3" t="n"/>
-      <c r="Q1162" s="3" t="n"/>
-      <c r="R1162" s="3" t="n"/>
-      <c r="S1162" s="3" t="n"/>
-      <c r="T1162" s="3" t="n"/>
-      <c r="U1162" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1162" s="7" t="n"/>
+      <c r="J1162" s="7" t="n"/>
+      <c r="K1162" s="7" t="n"/>
+      <c r="L1162" s="7" t="n"/>
+      <c r="M1162" s="7" t="n"/>
+      <c r="N1162" s="7" t="n"/>
+      <c r="O1162" s="7" t="n"/>
+      <c r="P1162" s="7" t="n"/>
+      <c r="Q1162" s="7" t="n"/>
+      <c r="R1162" s="7" t="n"/>
+      <c r="S1162" s="7" t="n"/>
+      <c r="T1162" s="7" t="n"/>
+      <c r="U1162" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1162" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Modernizare strazi și rețele tehnico-edi' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="1163">
-      <c r="A1163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C1163" s="2" t="inlineStr">
+      <c r="A1163" s="6" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="B1163" s="6" t="n"/>
+      <c r="C1163" s="6" t="inlineStr">
         <is>
           <t>Construire trotuar Colegiul Nicolae Cornateanu - cartier Baltag</t>
         </is>
       </c>
-      <c r="E1163" t="n">
+      <c r="D1163" s="6" t="n"/>
+      <c r="E1163" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F1163" t="inlineStr"/>
-      <c r="G1163" s="3" t="n"/>
-      <c r="H1163" s="3" t="n">
+      <c r="F1163" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1163" s="7" t="n"/>
+      <c r="H1163" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="I1163" s="3" t="n"/>
-      <c r="J1163" s="3" t="n"/>
-      <c r="K1163" s="3" t="n"/>
-      <c r="L1163" s="3" t="n"/>
-      <c r="M1163" s="3" t="n"/>
-      <c r="N1163" s="3" t="n"/>
-      <c r="O1163" s="3" t="n"/>
-      <c r="P1163" s="3" t="n"/>
-      <c r="Q1163" s="3" t="n"/>
-      <c r="R1163" s="3" t="n"/>
-      <c r="S1163" s="3" t="n"/>
-      <c r="T1163" s="3" t="n"/>
-      <c r="U1163" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1163" s="7" t="n"/>
+      <c r="J1163" s="7" t="n"/>
+      <c r="K1163" s="7" t="n"/>
+      <c r="L1163" s="7" t="n"/>
+      <c r="M1163" s="7" t="n"/>
+      <c r="N1163" s="7" t="n"/>
+      <c r="O1163" s="7" t="n"/>
+      <c r="P1163" s="7" t="n"/>
+      <c r="Q1163" s="7" t="n"/>
+      <c r="R1163" s="7" t="n"/>
+      <c r="S1163" s="7" t="n"/>
+      <c r="T1163" s="7" t="n"/>
+      <c r="U1163" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1163" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (39%): 'Construire trotuar Colegiul Nicolae Corn' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -51622,76 +51767,98 @@
       </c>
     </row>
     <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C1166" s="2" t="inlineStr">
+      <c r="A1166" s="6" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="B1166" s="6" t="n"/>
+      <c r="C1166" s="6" t="inlineStr">
         <is>
           <t>Amplasare statii de reincarcare vehicule electrice</t>
         </is>
       </c>
-      <c r="E1166" t="n">
+      <c r="D1166" s="6" t="n"/>
+      <c r="E1166" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F1166" t="inlineStr"/>
-      <c r="G1166" s="3" t="n"/>
-      <c r="H1166" s="3" t="n">
+      <c r="F1166" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1166" s="7" t="n"/>
+      <c r="H1166" s="7" t="n">
         <v>200000</v>
       </c>
-      <c r="I1166" s="3" t="n"/>
-      <c r="J1166" s="3" t="n"/>
-      <c r="K1166" s="3" t="n"/>
-      <c r="L1166" s="3" t="n"/>
-      <c r="M1166" s="3" t="n"/>
-      <c r="N1166" s="3" t="n"/>
-      <c r="O1166" s="3" t="n"/>
-      <c r="P1166" s="3" t="n"/>
-      <c r="Q1166" s="3" t="n"/>
-      <c r="R1166" s="3" t="n"/>
-      <c r="S1166" s="3" t="n"/>
-      <c r="T1166" s="3" t="n"/>
-      <c r="U1166" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1166" s="7" t="n"/>
+      <c r="J1166" s="7" t="n"/>
+      <c r="K1166" s="7" t="n"/>
+      <c r="L1166" s="7" t="n"/>
+      <c r="M1166" s="7" t="n"/>
+      <c r="N1166" s="7" t="n"/>
+      <c r="O1166" s="7" t="n"/>
+      <c r="P1166" s="7" t="n"/>
+      <c r="Q1166" s="7" t="n"/>
+      <c r="R1166" s="7" t="n"/>
+      <c r="S1166" s="7" t="n"/>
+      <c r="T1166" s="7" t="n"/>
+      <c r="U1166" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1166" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (42%): 'Amplasare statii de reincarcare vehicule' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="1167">
-      <c r="A1167" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C1167" s="2" t="inlineStr">
+      <c r="A1167" s="6" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="B1167" s="6" t="n"/>
+      <c r="C1167" s="6" t="inlineStr">
         <is>
           <t>Lucrari tehnico-edilitare și modernizare strazi din cartierele Sud-Vii și Mesteceni, municipiul Tulcea</t>
         </is>
       </c>
-      <c r="E1167" t="n">
+      <c r="D1167" s="6" t="n"/>
+      <c r="E1167" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F1167" t="inlineStr"/>
-      <c r="G1167" s="3" t="n"/>
-      <c r="H1167" s="3" t="n">
+      <c r="F1167" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1167" s="7" t="n"/>
+      <c r="H1167" s="7" t="n">
         <v>305000</v>
       </c>
-      <c r="I1167" s="3" t="n"/>
-      <c r="J1167" s="3" t="n"/>
-      <c r="K1167" s="3" t="n"/>
-      <c r="L1167" s="3" t="n"/>
-      <c r="M1167" s="3" t="n"/>
-      <c r="N1167" s="3" t="n"/>
-      <c r="O1167" s="3" t="n"/>
-      <c r="P1167" s="3" t="n"/>
-      <c r="Q1167" s="3" t="n"/>
-      <c r="R1167" s="3" t="n"/>
-      <c r="S1167" s="3" t="n"/>
-      <c r="T1167" s="3" t="n"/>
-      <c r="U1167" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1167" s="7" t="n"/>
+      <c r="J1167" s="7" t="n"/>
+      <c r="K1167" s="7" t="n"/>
+      <c r="L1167" s="7" t="n"/>
+      <c r="M1167" s="7" t="n"/>
+      <c r="N1167" s="7" t="n"/>
+      <c r="O1167" s="7" t="n"/>
+      <c r="P1167" s="7" t="n"/>
+      <c r="Q1167" s="7" t="n"/>
+      <c r="R1167" s="7" t="n"/>
+      <c r="S1167" s="7" t="n"/>
+      <c r="T1167" s="7" t="n"/>
+      <c r="U1167" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1167" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (44%): 'Lucrari tehnico-edilitare și modernizare' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -51733,39 +51900,50 @@
       </c>
     </row>
     <row r="1169">
-      <c r="A1169" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C1169" s="2" t="inlineStr">
+      <c r="A1169" s="6" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="B1169" s="6" t="n"/>
+      <c r="C1169" s="6" t="inlineStr">
         <is>
           <t>Mo ra ru   d carzin Municipiul Tulcea prin achizitionarea de vehicole nepoluante pentru transportul public - SMIS</t>
         </is>
       </c>
-      <c r="E1169" t="n">
+      <c r="D1169" s="6" t="n"/>
+      <c r="E1169" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="F1169" t="inlineStr"/>
-      <c r="G1169" s="3" t="n"/>
-      <c r="H1169" s="3" t="n">
+      <c r="F1169" s="6" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="G1169" s="7" t="n"/>
+      <c r="H1169" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="I1169" s="3" t="n"/>
-      <c r="J1169" s="3" t="n"/>
-      <c r="K1169" s="3" t="n"/>
-      <c r="L1169" s="3" t="n"/>
-      <c r="M1169" s="3" t="n"/>
-      <c r="N1169" s="3" t="n"/>
-      <c r="O1169" s="3" t="n"/>
-      <c r="P1169" s="3" t="n"/>
-      <c r="Q1169" s="3" t="n"/>
-      <c r="R1169" s="3" t="n"/>
-      <c r="S1169" s="3" t="n"/>
-      <c r="T1169" s="3" t="n"/>
-      <c r="U1169" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1169" s="7" t="n"/>
+      <c r="J1169" s="7" t="n"/>
+      <c r="K1169" s="7" t="n"/>
+      <c r="L1169" s="7" t="n"/>
+      <c r="M1169" s="7" t="n"/>
+      <c r="N1169" s="7" t="n"/>
+      <c r="O1169" s="7" t="n"/>
+      <c r="P1169" s="7" t="n"/>
+      <c r="Q1169" s="7" t="n"/>
+      <c r="R1169" s="7" t="n"/>
+      <c r="S1169" s="7" t="n"/>
+      <c r="T1169" s="7" t="n"/>
+      <c r="U1169" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="V1169" s="6" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (29%): 'Mo ra ru   d carzin Municipiul Tulcea pr' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -51815,7 +51993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F463"/>
+  <dimension ref="A1:F488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -59511,25 +59689,25 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B298" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C298" t="n">
         <v>35</v>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>est2027</t>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 0330-' in column est2027</t>
+          <t>name mismatch vs nomenclator (24%): 'Studii, PT,CF Consolidarea și Reabilitar' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
@@ -59549,37 +59727,37 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.01 0330-' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C300" t="n">
         <v>35</v>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>est2027</t>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>name mismatch vs nomenclator (36%): 'Studii, PT+ CF Consolidarea și reabilita' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -59599,12 +59777,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -59624,12 +59802,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -59674,12 +59852,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>unparseable cell '03.30- 71.01.01' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -59699,37 +59877,37 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B306" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C306" t="n">
         <v>35</v>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>est2027</t>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>name mismatch vs nomenclator (23%): 'Studii, PT,CF Consolidarea și Reabilitar' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
@@ -59749,37 +59927,37 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '03.30- 71.01.01' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B308" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C308" t="n">
         <v>35</v>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>est2027</t>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>unparseable cell '10.10.11 03.30-' in column est2027</t>
+          <t>name mismatch vs nomenclator (39%): 'Studii, PT,CF Consolidarea si Reabilitar' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
@@ -59879,7 +60057,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>unparseable cell '03.30-' in column est2027</t>
+          <t>unparseable cell '10.10.11 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -59899,12 +60077,12 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'Studi i ipi    i i i i pii Tulcea, Judeș' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (29%): 'Studii, PT,CF Consolidare și reabilitare' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -60004,32 +60182,32 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
+          <t>unparseable cell '03.30-' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B318" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C318" t="n">
         <v>35</v>
       </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>unparseable cell 'B8' in column total_2026</t>
+          <t>name mismatch vs nomenclator (50%): 'Studi i ipi    i i i i pii Tulcea, Judeș' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -60049,12 +60227,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60074,12 +60252,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60099,12 +60277,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.30 06.00-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60124,12 +60302,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60149,12 +60327,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>unparseable cell 'B8' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60174,12 +60352,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60199,12 +60377,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.30 07.00-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60224,12 +60402,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.30 06.00-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60249,12 +60427,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60274,12 +60452,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>unparseable cell 'CAP.74.02. PROTECTIAMEDIULUI' in column total_2026</t>
+          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60299,12 +60477,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>unparseable cell 'CAP.74.02. PROTECTIAMEDIULUI' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60324,12 +60502,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column total_2026</t>
+          <t>unparseable cell '71.01.30 07.00-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60349,12 +60527,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60374,12 +60552,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.01 03.30-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60399,12 +60577,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>unparseable cell '05.01- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'CAP.74.02. PROTECTIAMEDIULUI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60424,12 +60602,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>unparseable cell 'B8' in column total_2026</t>
+          <t>unparseable cell 'CAP.74.02. PROTECTIAMEDIULUI' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60449,12 +60627,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
+          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60474,12 +60652,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>unparseable cell 'CAP.84.02 TRANSPORTURI' in column total_2026</t>
+          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60499,12 +60677,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>unparseable cell 'CAP.84.02 TRANSPORTURI' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60524,12 +60702,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column total_2026</t>
+          <t>unparseable cell '05.01- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60549,12 +60727,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column est2027</t>
+          <t>unparseable cell 'B8' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60574,12 +60752,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>unparseable cell 'BL' in column total_2026</t>
+          <t>unparseable cell '71.01.30 50.00-' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60599,12 +60777,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'CAP.84.02 TRANSPORTURI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60624,12 +60802,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>unparseable cell 'BS' in column total_2026</t>
+          <t>unparseable cell 'CAP.84.02 TRANSPORTURI' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60649,12 +60827,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60670,7 +60848,7 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -60679,7 +60857,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'A. LUCRARI IN CONTINUARE' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60695,16 +60873,16 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'BL' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60720,7 +60898,7 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -60745,16 +60923,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>unparseable cell '03.02- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'BS' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60770,16 +60948,16 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>unparseable cell 'B.' in column total_2026</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60829,7 +61007,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71,01.30' in column est2027</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60874,12 +61052,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>unparseable cell 'C.' in column total_2026</t>
+          <t>unparseable cell '03.02- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60904,7 +61082,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>unparseable cell 'IV.' in column total_2026</t>
+          <t>unparseable cell 'B.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -60954,7 +61132,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell '03.03- 71,01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -60999,12 +61177,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>unparseable cell '120,00]' in column est2028</t>
+          <t>unparseable cell 'C.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61024,12 +61202,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
+          <t>unparseable cell 'IV.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61124,12 +61302,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>unparseable cell '50.00- 71.01.30' in column est2027</t>
+          <t>unparseable cell '120,00]' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61154,7 +61332,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>unparseable cell '50.00- 71.01.30' in column est2027</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61220,7 +61398,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -61229,7 +61407,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total 750,00' in column est2027</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61245,16 +61423,16 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total 750,00' in column est2028</t>
+          <t>unparseable cell '50.00- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61270,16 +61448,16 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total 750,00' in column est2029</t>
+          <t>unparseable cell '50.00- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61295,16 +61473,16 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>unparseable cell '50.00-566602' in column est2028</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61320,7 +61498,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -61329,7 +61507,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total ：300,00' in column est2027</t>
+          <t>unparseable cell '03.03- 71.01.30' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61349,12 +61527,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total ：300,00' in column est2028</t>
+          <t>unparseable cell 'Total 750,00' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61374,12 +61552,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>unparseable cell 'Total ：300,00' in column est2029</t>
+          <t>unparseable cell 'Total 750,00' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61399,12 +61577,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>unparseable cell 'A' in column total_2026</t>
+          <t>unparseable cell 'Total 750,00' in column est2029</t>
         </is>
       </c>
     </row>
@@ -61424,12 +61602,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>unparseable cell 'Buget stat 13%' in column est2027</t>
+          <t>unparseable cell '50.00-566602' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61449,12 +61627,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>unparseable cell '03.02-564801' in column est2028</t>
+          <t>unparseable cell 'Total ：300,00' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61474,12 +61652,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>unparseable cell 'FEDR 85%' in column est2027</t>
+          <t>unparseable cell 'Total ：300,00' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61499,12 +61677,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>unparseable cell '03.02-564802' in column est2028</t>
+          <t>unparseable cell 'Total ：300,00' in column est2029</t>
         </is>
       </c>
     </row>
@@ -61524,12 +61702,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>unparseable cell 'Buget local 2%' in column est2027</t>
+          <t>unparseable cell 'A' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61549,12 +61727,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>unparseable cell '03.02-564803' in column est2028</t>
+          <t>unparseable cell 'Buget stat 13%' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61574,12 +61752,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>unparseable cell '14:160,00 Total' in column est2027</t>
+          <t>unparseable cell '03.02-564801' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61599,12 +61777,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>unparseable cell '14:160,00 Total' in column est2028</t>
+          <t>unparseable cell 'FEDR 85%' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61624,12 +61802,12 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>unparseable cell '14:160,00 Total' in column est2029</t>
+          <t>unparseable cell '03.02-564802' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61645,16 +61823,16 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column total_2026</t>
+          <t>unparseable cell 'Buget local 2%' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61670,16 +61848,16 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column est2027</t>
+          <t>unparseable cell '03.02-564803' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61695,16 +61873,16 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column est2028</t>
+          <t>unparseable cell '14:160,00 Total' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61720,16 +61898,16 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>unparseable cell 'A' in column total_2026</t>
+          <t>unparseable cell '14:160,00 Total' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61745,16 +61923,16 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>unparseable cell '50.00-60.01' in column est2027</t>
+          <t>unparseable cell '14:160,00 Total' in column est2029</t>
         </is>
       </c>
     </row>
@@ -61774,12 +61952,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>unparseable cell '50.00-60.03' in column est2027</t>
+          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61789,22 +61967,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>44</v>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>67.02</t>
+        <v>41</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>duplicate of p42 with different values</t>
+          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61814,22 +61992,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B390" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>44</v>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>70.02</t>
+        <v>41</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>duplicate of p42 with different values</t>
+          <t>unparseable cell 'AP.84.02TRANSPORTURI' in column est2028</t>
         </is>
       </c>
     </row>
@@ -61839,22 +62017,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>44</v>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>84.02</t>
+        <v>41</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>duplicate of p42 with different values</t>
+          <t>unparseable cell 'A' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -61870,7 +62048,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -61879,7 +62057,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>unparseable cell 'SUMA ALOCATÃ' in column est2027</t>
+          <t>unparseable cell '50.00-60.01' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61895,16 +62073,16 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. CULTURÃ' in column total_2026</t>
+          <t>unparseable cell '50.00-60.03' in column est2027</t>
         </is>
       </c>
     </row>
@@ -61914,22 +62092,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B394" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>46</v>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>est2027</t>
+        <v>44</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>unparseable cell 'A. CULTURÃ' in column est2027</t>
+          <t>duplicate of p42 with different values</t>
         </is>
       </c>
     </row>
@@ -61939,22 +62117,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B395" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>46</v>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>44</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>unparseable cell '1.' in column total_2026</t>
+          <t>duplicate of p42 with different values</t>
         </is>
       </c>
     </row>
@@ -61964,22 +62142,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B396" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>46</v>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>44</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>unparseable cell '2.' in column total_2026</t>
+          <t>duplicate of p42 with different values</t>
         </is>
       </c>
     </row>
@@ -61999,12 +62177,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>unparseable cell '2.' in column total_2026</t>
+          <t>unparseable cell 'SUMA ALOCATÃ' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62029,7 +62207,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>unparseable cell '2.' in column total_2026</t>
+          <t>unparseable cell 'A. CULTURÃ' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62049,12 +62227,12 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>unparseable cell '3.' in column total_2026</t>
+          <t>unparseable cell 'A. CULTURÃ' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62070,7 +62248,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -62079,7 +62257,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>unparseable cell '4.' in column total_2026</t>
+          <t>unparseable cell '1.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62095,16 +62273,16 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>unparseable cell '15 septembrie – 22 septembrie' in column est2027</t>
+          <t>unparseable cell '2.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62120,7 +62298,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -62129,7 +62307,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>unparseable cell '5.' in column total_2026</t>
+          <t>unparseable cell '2.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62145,16 +62323,16 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>unparseable cell 'Pe tot parcursul anului' in column est2027</t>
+          <t>unparseable cell '2.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62170,16 +62348,16 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>unparseable cell '30 mai – 1 iunie' in column est2027</t>
+          <t>unparseable cell '3.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62195,7 +62373,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -62204,7 +62382,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>unparseable cell '7.' in column total_2026</t>
+          <t>unparseable cell '4.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62220,7 +62398,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -62229,7 +62407,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>unparseable cell 'An accidental forever”' in column est2027</t>
+          <t>unparseable cell '15 septembrie – 22 septembrie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62245,16 +62423,16 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>unparseable cell '1 iunie – 30 septembrie' in column est2028</t>
+          <t>unparseable cell '5.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62270,16 +62448,16 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>unparseable cell 'SUBTOTAL B' in column total_2026</t>
+          <t>unparseable cell 'Pe tot parcursul anului' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62295,16 +62473,16 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>unparseable cell '1.' in column total_2026</t>
+          <t>unparseable cell '30 mai – 1 iunie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62324,12 +62502,12 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>unparseable cell '1-17 mai' in column est2027</t>
+          <t>unparseable cell '7.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62354,7 +62532,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>unparseable cell '1-17 mai' in column est2027</t>
+          <t>unparseable cell 'An accidental forever”' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62370,16 +62548,16 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>unparseable cell '16-22 septembrie' in column est2027</t>
+          <t>unparseable cell '1 iunie – 30 septembrie' in column est2028</t>
         </is>
       </c>
     </row>
@@ -62395,16 +62573,16 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>unparseable cell 'lunie-octombrie' in column est2027</t>
+          <t>unparseable cell 'SUBTOTAL B' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62420,16 +62598,16 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>unparseable cell 'mai-iunie' in column est2027</t>
+          <t>unparseable cell '1.' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62445,7 +62623,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -62454,7 +62632,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>unparseable cell 'mai-octombrie' in column est2027</t>
+          <t>unparseable cell '1-17 mai' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62470,7 +62648,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -62479,7 +62657,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>unparseable cell '25 august-5 septembrie' in column est2027</t>
+          <t>unparseable cell '1-17 mai' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62504,7 +62682,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>unparseable cell 'lunie - octombrie' in column est2027</t>
+          <t>unparseable cell '16-22 septembrie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62520,16 +62698,16 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>unparseable cell 'SUBTOTAL D' in column total_2026</t>
+          <t>unparseable cell 'lunie-octombrie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62545,16 +62723,16 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>unparseable cell 'SUBTOTAL E' in column total_2026</t>
+          <t>unparseable cell 'mai-iunie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62570,16 +62748,16 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>unparseable cell 'Buget stat' in column total_2026</t>
+          <t>unparseable cell 'mai-octombrie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62595,7 +62773,7 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -62604,7 +62782,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>unparseable cell 'Buget local' in column est2027</t>
+          <t>unparseable cell '25 august-5 septembrie' in column est2027</t>
         </is>
       </c>
     </row>
@@ -62620,91 +62798,91 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>unparseable cell 'TOTAL' in column est2028</t>
+          <t>unparseable cell 'lunie - octombrie' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B423" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>51</v>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>50</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Colegiul Agricol Nicolae Cornateanu Tulc' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell 'SUBTOTAL D' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B424" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>51</v>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>20</t>
+        <v>50</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Cresa Sibell' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>unparseable cell 'SUBTOTAL E' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B425" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>53</v>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>51</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Dotarea cu mobilier, materiale didactice' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell 'Buget stat' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -62714,29 +62892,29 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>53</v>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>51</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>duplicate of p51 with different values</t>
+          <t>unparseable cell 'Buget local' in column est2027</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
@@ -62745,203 +62923,203 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>53</v>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>11</t>
+        <v>51</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>code 11 (expense_functional) not in nomenclator</t>
+          <t>unparseable cell 'TOTAL' in column est2028</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B428" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>code 12 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (38%): 'Colegiul Agricol Nicolae Cornateanu Tulc' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>code 13 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (42%): 'Colegiul Anghel Saligny Tulcea' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B430" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>code 14 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (40%): 'Scoala Gimnaziala Nifon Balasescu Tulcea' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B431" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>code 15 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'Scoala Gimnaziala Elena Doamna Tulcea' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B432" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>code 16 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (35%): 'Scoala Gimnaziala Constantin Gavenea Tul' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B433" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>code 17 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (41%): 'Scoala Gimnaziala loan Nenitescu Tulcea' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B434" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>code 18 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (35%): 'Cresa Sibell' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B435" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -62949,19 +63127,19 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>code 19 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (31%): 'Dotarea cu mobilier, materiale didactice' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -62974,19 +63152,19 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Alte active fixe - Liceul Henri Coanda' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -62999,24 +63177,24 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>duplicate of p51 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Container modular - Liceul Grigore Moisi' vs 'Sume defalcate din TVA'</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B438" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -63024,24 +63202,24 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>code 21 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B439" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -63049,24 +63227,24 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>code 22 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (40%): 'Laptopuri 10 buc - Liceul Grigore Moisil' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B440" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -63074,12 +63252,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>code 23 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -63099,12 +63277,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>code 24 (expense_functional) not in nomenclator</t>
+          <t>code 13 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -63124,187 +63302,187 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>code 25 (expense_functional) not in nomenclator</t>
+          <t>code 14 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B443" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>code 26 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (36%): 'Table interactive - 3 buc - Scoala gimna' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B444" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>code 27 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B445" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>code 28 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'Table inteligente - Scoala gimnaziala Nr' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B446" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>code 29 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B447" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Reabilitare si modernizare Colegiul Dobr' vs 'TITLUL III DOBANZI'</t>
+          <t>code 17 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B448" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>code 31 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (38%): 'Masini de gatit pe gaz - 2 buc - Liceul ' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B449" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>code 32 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -63320,66 +63498,66 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>code 33 (expense_functional) not in nomenclator</t>
+          <t>code 19 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B451" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>code 34.35 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (36%): 'Alte active fixe - Liceul Henri Coanda' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B452" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>code 36 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p51 with different values</t>
         </is>
       </c>
     </row>
@@ -63395,46 +63573,41 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>code 37 (expense_functional) not in nomenclator</t>
+          <t>code 21 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B454" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>code 22 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -63450,16 +63623,16 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>code 38 (expense_functional) not in nomenclator</t>
+          <t>code 23 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -63475,23 +63648,23 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>code 39 (expense_functional) not in nomenclator</t>
+          <t>code 24 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
@@ -63500,28 +63673,28 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>54</v>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>53</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>unparseable cell '100.000,00 30.000,00' in column total_2026</t>
+          <t>code 25 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B458" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -63529,19 +63702,19 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Studii SF, PT Amenajare loc de joacă Nep' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
+          <t>code 26 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
@@ -63552,26 +63725,26 @@
       <c r="C459" t="n">
         <v>54</v>
       </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>unparseable cell '480.000,00 241.000,00' in column total_2026</t>
+          <t>code 27 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B460" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -63579,44 +63752,44 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'municipiul Tulcea' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>code 28 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B461" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Centru de zi de asistenta si recuperare ' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>code 29 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -63625,16 +63798,16 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>duplicate of p54 with different values</t>
+          <t>name mismatch vs nomenclator (34%): 'Reabilitare si modernizare Colegiul Dobr' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
@@ -63650,16 +63823,646 @@
         </is>
       </c>
       <c r="C463" t="n">
+        <v>54</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>31.02</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Studii,SF, Construire Cresa cartier E3, ' vs 'Venituri din dobanzi'</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B464" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>54</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>code 32 (expense_functional) not in nomenclator</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>54</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>33.02</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Modernizarea infrastructurii scolare pri' vs 'Venituri din prestari de servicii si alt'</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B466" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>54</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>code 34.35 (expense_functional) not in nomenclator</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>54</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>36.02</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (15%): 'Stagii de practica pt elevi in Delta Dun' vs 'Diverse venituri'</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>54</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>37.02</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'George Georgescu, str. Babadag, nr. 138,' vs 'Transferuri voluntare,  altele decat sub'</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>V6_repair</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>54</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>37.02</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>cell re-read from image (unverified transcription)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B470" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>54</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>code 38 (expense_functional) not in nomenclator</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>54</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>39.02</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Reabilitare si modernizare Scoala I.L.Ca' vs 'Venituri din valorificarea unor bunuri'</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B472" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>54</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>unparseable cell '100.000,00 30.000,00' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>54</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>34.02</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (41%): 'Amenajare teren sintetic stadion Cozma Z' vs 'Venituri din taxe administrative, eliber'</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>54</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Studii SF, PT Amenajare loc de joacă Nep' vs 'Titlul VIII PROIECTE CU FINANTARE DIN FO'</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B475" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>54</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>unparseable cell '480.000,00 241.000,00' in column total_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>54</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (38%): 'municipiul Tulcea' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>55</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (42%): 'Centru de zi de asistenta si recuperare ' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>55</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>duplicate of p54 with different values</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>55</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (30%): 'Centru comunitar integrat, Municipiul Tu' vs 'Sume defalcate din TVA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>55</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (37%): 'Elaborare studiu de fezabilitate constru' vs 'Alte impozite si taxe generale pe bunuri'</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>55</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (24%): 'Centru de recuperare neuromotorie de tip' vs 'Taxe pe servicii specifice'</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>55</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (40%): 'Centru de zi pentru persoane adulte cu d' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
         <v>58</v>
       </c>
-      <c r="D463" t="inlineStr">
+      <c r="D483" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr">
+      <c r="F483" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (35%): 'Reabilitare/Modernizare sistem rutier si' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>58</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (31%): 'Modernizare strazi și rețele tehnico-edi' vs 'Sume defalcate din TVA'</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>58</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (39%): 'Construire trotuar Colegiul Nicolae Corn' vs 'Alte impozite si taxe generale pe bunuri'</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>58</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (42%): 'Amplasare statii de reincarcare vehicule' vs 'Taxe pe servicii specifice'</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>58</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (44%): 'Lucrari tehnico-edilitare și modernizare' vs 'Taxe pe utilizarea bunurilor, autorizare'</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>58</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>name mismatch vs nomenclator (29%): 'Mo ra ru   d carzin Municipiul Tulcea pr' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -63710,7 +64513,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4">
@@ -63730,7 +64533,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.7</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6">
@@ -63740,7 +64543,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -63750,7 +64553,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8">
